--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -622,16 +622,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;rules&gt;
-&lt;structureObjectRule&gt;
+          <t>&lt;structureObjectRule&gt;
             &lt;objectPath allowedObjectFlag="0"&gt;//randomList//randomList&lt;/objectPath&gt;
             &lt;objectUse&gt;BRDP-S1-00507. A &amp;lt;randomList&amp;gt; must not be nested inside another &amp;lt;randomList&amp;gt; -- the default prefix pf02 is always used, without nesting. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;
 &lt;nonContextRule&gt;
           &lt;simplePara&gt;BRDP-S1-00507. Decide whether to use a consistent set of prefixes for random list throughout the project. &lt;/simplePara&gt;
           &lt;simplePara&gt;Decision made by Project. Nested randomList should be avoided. The listItemPrefix attribute shall always be the default value, which is pf02.&lt;/simplePara&gt;
-        &lt;/nonContextRule&gt;
-&lt;/rules&gt;</t>
+        &lt;/nonContextRule&gt;</t>
         </is>
       </c>
     </row>
@@ -708,8 +706,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;structureObjectRuleGroup&gt;
-&lt;structureObjectRule&gt;
+          <t>&lt;structureObjectRule&gt;
             &lt;objectPath allowedObjectFlag="1"&gt;//responsiblePartnerCompany/@enterpriseCode&lt;/objectPath&gt;
             &lt;objectUse&gt;BRDP-S1-00070. The responsible partner company's enterpriseCode must be C1008 (Lufthansa Technik AG's CAGE code). &lt;/objectUse&gt;
             &lt;objectValue valueForm="single" valueAllowed="C1008"&gt;CAGE code for LUFTHANSA TECHNIK AG is C1008&lt;/objectValue&gt;
@@ -718,8 +715,7 @@
             &lt;objectPath allowedObjectFlag="1"&gt;//responsiblePartnerCompany/enterpriseName&lt;/objectPath&gt;
             &lt;objectUse&gt;BRDP-S1-00070. The responsible partner company's enterpriseName must be 'LUFTHANSA TECHNIK AG'. &lt;/objectUse&gt;
             &lt;objectValue valueForm="single" valueAllowed="LUFTHANSA TECHNIK AG"&gt;Enterprise Name is LUFTHANSA TECHNIK AG&lt;/objectValue&gt;
-          &lt;/structureObjectRule&gt;
-&lt;/structureObjectRuleGroup&gt;</t>
+          &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -626,6 +626,10 @@
             &lt;objectPath allowedObjectFlag="0"&gt;//randomList//randomList&lt;/objectPath&gt;
             &lt;objectUse&gt;BRDP-S1-00507. A &amp;lt;randomList&amp;gt; must not be nested inside another &amp;lt;randomList&amp;gt; -- the default prefix pf02 is always used, without nesting. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;
+&lt;structureObjectRule&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//randomList[@listItemPrefix != 'pf02']&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00507. The attribute listItemPrefix of a &amp;lt;randomList&amp;gt; must be pf02, the default prefix (a &amp;lt;randomList&amp;gt; without the attribute uses pf02). &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;
 &lt;nonContextRule&gt;
           &lt;simplePara&gt;BRDP-S1-00507. Decide whether to use a consistent set of prefixes for random list throughout the project. &lt;/simplePara&gt;
           &lt;simplePara&gt;Decision made by Project. Nested randomList should be avoided. The listItemPrefix attribute shall always be the default value, which is pf02.&lt;/simplePara&gt;
@@ -676,22 +680,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRDP-S1-00070</t>
+          <t>BRDP-S1-00187</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Use of the element &lt;enterpriseName&gt; and/or the attribute enterpriseCode for the responsible partner company</t>
+          <t>Minimum number of substeps in a step</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Decide whether to use the element &lt;enterpriseName&gt; and/or the attribute enterpriseCode to capture the name and CAGE code, respectively, of the responsible partner company. If the name is used it must be done consistently and be mandatory for the project.</t>
+          <t>Decide whether to allow for a single substep, or to insist on a minimum of two substeps in a step.
+Note
+The Schema allows for a single substep.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAGE C1008, enterprise name: 'LUFTHANSA TECHNIK AG'</t>
+          <t>A minimum of two sub-steps is required</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -707,14 +713,8 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="1"&gt;//responsiblePartnerCompany/@enterpriseCode&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00070. The responsible partner company's enterpriseCode must be C1008 (Lufthansa Technik AG's CAGE code). &lt;/objectUse&gt;
-            &lt;objectValue valueForm="single" valueAllowed="C1008"&gt;CAGE code for LUFTHANSA TECHNIK AG is C1008&lt;/objectValue&gt;
-          &lt;/structureObjectRule&gt;
-&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="1"&gt;//responsiblePartnerCompany/enterpriseName&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00070. The responsible partner company's enterpriseName must be 'LUFTHANSA TECHNIK AG'. &lt;/objectUse&gt;
-            &lt;objectValue valueForm="single" valueAllowed="LUFTHANSA TECHNIK AG"&gt;Enterprise Name is LUFTHANSA TECHNIK AG&lt;/objectValue&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(proceduralStep) = 1]&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00187. A &amp;lt;proceduralStep&amp;gt; that has substeps must have at least two -- a single substep is not allowed. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;</t>
         </is>
       </c>

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -540,7 +540,7 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="1"&gt;//@assyCode[matches(., '^\d{2}$')]&lt;/objectPath&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//@assyCode[not(matches(., '^\d{2}$'))]&lt;/objectPath&gt;
             &lt;objectUse&gt;BRDP-S1-00338. The assembly code (@assyCode) must be exactly two digits. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;</t>
         </is>

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -540,8 +540,8 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="0"&gt;//@assyCode[not(matches(., '^\d{2}$'))]&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00338. The assembly code (@assyCode) must be exactly two digits. &lt;/objectUse&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//@assyCode[string-length(.) != 2]&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00338. The assembly code (@assyCode) must be exactly two characters. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;</t>
         </is>
       </c>

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -509,35 +509,115 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>BRDP-S1-00095</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Use of the element &lt;internalRef&gt; in titles</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Use of the element &lt;internalRef&gt; in titles is strongly discouraged. However, decide whether to use cross-references in titles.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The element &lt;internalRef&gt; shall not be used</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//title/internalRef&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00095. The element &amp;lt;internalRef&amp;gt; must not be used within titles.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BRDP-S1-00150</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Use of the attribute id on the element &lt;supportEquipDescr&gt; in the element &lt;preliminaryRqmts&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Decide whether to link from the body of the procedure to the support equipment listed in Preliminary requirements. Note: The attribute id on the element &lt;supportEquipDescr&gt; is used to establish the link between the two and will guarantee consistent use of identification throughout the procedure. The use of cross-references is encouraged.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Use of the attribute id on the element &lt;supportEquipDescr&gt; in the element &lt;preliminaryRqmts&gt; is required.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//supportEquipDescr[not(@id)]&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00150. Every &amp;lt;supportEquipDescr&amp;gt; in Preliminary Requirements must carry an id attribute, to allow cross-referencing from the procedure to the listed support equipment.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>BRDP-S1-00338</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Number of characters in assembly code</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Decide whether to use two or four characters for unit or assembly.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Two characters to be used</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
             &lt;objectPath allowedObjectFlag="0"&gt;//@assyCode[string-length(.) != 2]&lt;/objectPath&gt;
@@ -546,81 +626,211 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00065</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Use of the element &lt;copyright&gt; and source of copyright information</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Decide whether and how to use the element &lt;copyright&gt;. Any copyright information must be obtained from the relevant authority.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Projects creating their own documentation shall have the copyright incorporated: "Copyright © 2024 by Lufthansa Technik AG.
-This document and its content are copyright protected and either owned by or licensed to Lufthansa Technik AG. All rights reserved. This document and the information contained herein shall be kept strictly confidential and shall not be used, disclosed to others or reproduced for any use other than the one they were provided for without the express written consent of Lufthansa Technik AG."</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BRDP-S1-00334</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Allocation of system difference code</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Decide which system difference code values to be used for the Product.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No need for SDC seen, use default. SDC to be used if different LRUs are in identical SNS.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="1"&gt;//copyright/copyrightPara/emphasis[1]&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00065. Projects with their own documentation must include the Lufthansa Technik AG copyright notice, opening with 'Copyright (C) 2024'. &lt;/objectUse&gt;
-            &lt;objectValue valueForm="single" valueAllowed="Copyright (C) 2024"&gt;Lufthansa Technik copyright emphasis&lt;/objectValue&gt;
+  &lt;objectPath allowedObjectFlag="2"&gt;//@systemDiffCode&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) should be 'A', used only when different LRUs share an identical SNS; no UOC is used.&lt;/objectUse&gt;
+  &lt;objectValue valueForm="single" valueAllowed="A"&gt;SDC to be used if different LRUs are in identical SNS. No UOC is used.&lt;/objectValue&gt;
+  &lt;objectValue valueForm="single" valueAllowed="F"&gt;Only the S1000D and ATA BREX data modules use systemDiffCode F.&lt;/objectValue&gt;
+&lt;/structureObjectRule&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRDP-S1-00316</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Use of the element &lt;applic&gt; in the data module status and content</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Decide how to use the element &lt;applic&gt; and to populate its child elements and attributes across the project or the organization.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Use &lt;applic&gt; element</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//dmStatus/applicRef | //pmStatus/applicRef&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00316. Data module and publication module status must use the &amp;lt;applic&amp;gt; element directly, not &amp;lt;applicRef&amp;gt;.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BRDP-S1-00187</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Minimum number of substeps in a step</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Decide whether to allow for a single substep, or to insist on a minimum of two substeps in a step.
+Note
+The Schema allows for a single substep.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A minimum of two sub-steps is required</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>&lt;structureObjectRule&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(proceduralStep) = 1]&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00187. A &amp;lt;proceduralStep&amp;gt; that has substeps must have at least two -- a single substep is not allowed. &lt;/objectUse&gt;
           &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRDP-S1-00120</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Use of titles for the elements &lt;levelledPara&gt; and &lt;proceduralStep&gt; from sublevel six thru eight for legacy data</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Decide whether titles can be included for the elements &lt;levelledPara&gt; and &lt;proceduralStep&gt; from sublevel six thru eight when converting legacy data to S1000D.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>There will be a maximum of five levels, while the fifth level must not have a title.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(ancestor-or-self::proceduralStep) &amp;gt; 5] | //levelledPara[count(ancestor-or-self::levelledPara) &amp;gt; 5]&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00120. A maximum of five levels of &amp;lt;proceduralStep&amp;gt; and &amp;lt;levelledPara&amp;gt; is allowed.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;
+&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(ancestor-or-self::proceduralStep) = 5]/title | //levelledPara[count(ancestor-or-self::levelledPara) = 5]/title&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00120. A &amp;lt;proceduralStep&amp;gt; or &amp;lt;levelledPara&amp;gt; at level five must not have a &amp;lt;title&amp;gt;.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;
+&lt;nonContextRule&gt;
+  &lt;simplePara&gt;BRDP-S1-00120. Decide whether titles can be included for the elements &amp;lt;levelledPara&amp;gt; and &amp;lt;proceduralStep&amp;gt; from sublevel six thru eight when converting legacy data to S1000D.&lt;/simplePara&gt;
+  &lt;simplePara&gt;Decision made by Project. There will be a maximum of five levels, while the fifth level must not have a title.&lt;/simplePara&gt;
+&lt;/nonContextRule&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>BRDP-S1-00507</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Prefixes to be used for random lists at presentation</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Decide whether to use a consistent set of prefixes for random list throughout the project.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>The default prefix (pf02) shall be used/presented.
 Nested randomList should be avoided. The listItemPrefix attribute shall always be the default value, which is pf02.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
             &lt;objectPath allowedObjectFlag="0"&gt;//randomList//randomList&lt;/objectPath&gt;
@@ -637,318 +847,49 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00053</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Data module change/revised ratio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Decide on the threshold that a data module is considered revised rather than changed.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Revised shall never be used. All changed data modules shall be marked as "changed" and the corresponding change marks be set.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="0"&gt;//@issueType[.='revised']&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00053. The issueType attribute must never be set to 'revised' -- all changed data modules are marked 'changed' with change marks; revised is not used. &lt;/objectUse&gt;
-          &lt;/structureObjectRule&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00187</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Minimum number of substeps in a step</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Decide whether to allow for a single substep, or to insist on a minimum of two substeps in a step.
-Note
-The Schema allows for a single substep.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A minimum of two sub-steps is required</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>&lt;structureObjectRule&gt;
-            &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(proceduralStep) = 1]&lt;/objectPath&gt;
-            &lt;objectUse&gt;BRDP-S1-00187. A &amp;lt;proceduralStep&amp;gt; that has substeps must have at least two -- a single substep is not allowed. &lt;/objectUse&gt;
-          &lt;/structureObjectRule&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>BRDP-S1-00219</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Use of the element &lt;partSegment&gt; in the element &lt;itemSeqNumber&gt;</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Decide whether to use the element &lt;partSegment&gt; to store the part data in the IPD data module each time the part is listed, or store the part data once externally in the part CIR data module.
 Note
 The element &lt;partSegment&gt; must be used for S2000M IPD data modules.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>&lt;partSegment&gt; shall be used.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/ipd.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="1"&gt;//itemSeqNumber/partSegment&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00219. The element &amp;lt;partSegment&amp;gt; must be used within &amp;lt;itemSeqNumber&amp;gt; to store part data in IPD data modules. &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BRDP-EXT-00001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Define security classification values and terms (attribute securityClassification)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Decide which values to use for the attribute securityClassification and allocate suitable definitions. Refer to Chap 3.9.6.1.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00012 does not exist in S1000D 4.2. Not to take into account.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>&lt;nonContextRule&gt;
-          &lt;simplePara&gt;This corresponds to BRDP-S1-00012 and it does not exist in S1000D 4.2. Not to take into account. &lt;/simplePara&gt;
-        &lt;/nonContextRule&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00006</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Schemas to be used</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Decide which Schemas to be used and in which information set they are to be used.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Descriptive, Procedural and IPD schemas shall be used as per Writing Style Guide</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//@xsi:noNamespaceSchemaLocation&lt;/objectPath&gt;
-                  &lt;objectUse&gt;BRDP-S1-00006. The applicability cross-reference table schema location should be the flat S1000D 4.2 appliccrossreftable.xsd. &lt;/objectUse&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/appliccrossreftable.xsd"&gt;Applicability schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/brex.xsd"&gt;BREX schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/comrep.xsd"&gt;CIR schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/condcrossreftable.xsd"&gt;Condition schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/ddn.xsd"&gt;DDN schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/descript.xsd"&gt;Descriptive schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/dml.xsd"&gt;DML schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/fault.xsd"&gt;Fault schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/ipd.xsd"&gt;IPD schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/pm.xsd"&gt;PM schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/prdcrossreftable.xsd"&gt;Product schema flat 4.2&lt;/objectValue&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/proced.xsd"&gt;Procedural schema flat 4.2&lt;/objectValue&gt;
-               &lt;/structureObjectRule&gt;
-&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/condcrossreftable.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="0"&gt;//dmodule&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00006. Condition cross-reference table data modules must use the Descriptive, Procedural or IPD schema, per the project's schema decision (Writing Style Guide). &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;
-&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/fault.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="0"&gt;//dmodule&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00006. Fault data modules must use the Descriptive, Procedural or IPD schema, per the project's schema decision (Writing Style Guide). &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;
-&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/prdcrossreftable.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="0"&gt;//dmodule&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00006. Product cross-reference table data modules must use the Descriptive, Procedural or IPD schema, per the project's schema decision (Writing Style Guide). &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BRDP-S1-00377</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Types of CIR data modules to be used</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Decide which CIR data module types to be used. In order to avoid any redundancy and inconsistency, care must be paid on some types, depending on other project specific decisions, for example tailoring of the S2000M (IPD data modules vs parts CIR data module).</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CIR concept shall be used for warnings, cautions, tools, enterprise codes, parts (for IPL), supplies</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-2/xml_schema_flat/comrep.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                            &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/partRepository&lt;/objectPath&gt;
-                            &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include a &amp;lt;partRepository&amp;gt; -- CIR is used for parts (IPL). &lt;/objectUse&gt;
-                         &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                            &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/toolRepository&lt;/objectPath&gt;
-                            &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include a &amp;lt;toolRepository&amp;gt; -- CIR is used for tools. &lt;/objectUse&gt;
-                         &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                            &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/supplyRepository&lt;/objectPath&gt;
-                            &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include a &amp;lt;supplyRepository&amp;gt; -- CIR is used for supplies. &lt;/objectUse&gt;
-                         &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                            &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/warningRepository&lt;/objectPath&gt;
-                            &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include a &amp;lt;warningRepository&amp;gt; -- CIR is used for warnings. &lt;/objectUse&gt;
-                         &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                            &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/cautionRepository&lt;/objectPath&gt;
-                            &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include a &amp;lt;cautionRepository&amp;gt; -- CIR is used for cautions. &lt;/objectUse&gt;
-                         &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="2"&gt;//commonRepository/enterpriseRepository&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00377. The Common Information Repository may include an &amp;lt;enterpriseRepository&amp;gt; -- CIR is used for enterprise codes. &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="0"&gt;//commonRepository/supplyRqmtRepository&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00377. The element &amp;lt;supplyRqmtRepository&amp;gt; must not be used in the Common Information Repository -- CIR is scoped to warnings, cautions, tools, enterprise codes, parts and supplies only. &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-          &lt;structureObjectRule&gt;
-                      &lt;objectPath allowedObjectFlag="0"&gt;//commonRepository/applicRepository&lt;/objectPath&gt;
-                      &lt;objectUse&gt;BRDP-S1-00377. The element &amp;lt;applicRepository&amp;gt; must not be used in the Common Information Repository -- CIR is scoped to warnings, cautions, tools, enterprise codes, parts and supplies only. &lt;/objectUse&gt;
-                    &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+  &lt;structureObjectRuleGroup&gt;
+    &lt;structureObjectRule&gt;
+      &lt;objectPath allowedObjectFlag="0"&gt;//itemSeqNumber[not(partSegment)]&lt;/objectPath&gt;
+      &lt;objectUse&gt;BRDP-S1-00219. Every &amp;lt;itemSeqNumber&amp;gt; must contain &amp;lt;partSegment&amp;gt; to store the part data in IPD data modules.&lt;/objectUse&gt;
+    &lt;/structureObjectRule&gt;
+  &lt;/structureObjectRuleGroup&gt;
+&lt;/contextRules&gt;</t>
         </is>
       </c>
     </row>

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -559,7 +559,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Decide whether to link from the body of the procedure to the support equipment listed in Preliminary requirements. Note: The attribute id on the element &lt;supportEquipDescr&gt; is used to establish the link between the two and will guarantee consistent use of identification throughout the procedure. The use of cross-references is encouraged.</t>
+          <t>Decide whether to link from the body of the procedure to the support equipment listed in Preliminary requirements.
+Note
+The attribute id on the element &lt;supportEquipDescr&gt; is used to establish the link between the two and will guarantee consistent use of identification throughout the procedure. The use of cross-references is encouraged.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/public/brdp-template-4-2.xlsx
+++ b/public/brdp-template-4-2.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No need for SDC seen, use default. SDC to be used if different LRUs are in identical SNS.</t>
+          <t>No need for SDC seen, use default A.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -663,9 +663,8 @@
         <is>
           <t>&lt;structureObjectRule&gt;
   &lt;objectPath allowedObjectFlag="2"&gt;//@systemDiffCode&lt;/objectPath&gt;
-  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) should be 'A', used only when different LRUs share an identical SNS; no UOC is used.&lt;/objectUse&gt;
+  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) must be 'A'; no UOC is used.&lt;/objectUse&gt;
   &lt;objectValue valueForm="single" valueAllowed="A"&gt;SDC to be used if different LRUs are in identical SNS. No UOC is used.&lt;/objectValue&gt;
-  &lt;objectValue valueForm="single" valueAllowed="F"&gt;Only the S1000D and ATA BREX data modules use systemDiffCode F.&lt;/objectValue&gt;
 &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
